--- a/tables/xls/it/90_Brogliaccio.xlsx
+++ b/tables/xls/it/90_Brogliaccio.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
   <si>
     <t>Data/ora</t>
   </si>
   <si>
+    <t>Servizio</t>
+  </si>
+  <si>
     <t>Descrizione</t>
   </si>
   <si>
@@ -33,103 +36,109 @@
     <t>Tipo</t>
   </si>
   <si>
+    <t>Elenco di valori (separati da virgola)</t>
+  </si>
+  <si>
+    <t>Dim. massima</t>
+  </si>
+  <si>
+    <t>Obbligatorio</t>
+  </si>
+  <si>
+    <t>Valore predefinito</t>
+  </si>
+  <si>
+    <t>Sola lettura</t>
+  </si>
+  <si>
+    <t>Visibile</t>
+  </si>
+  <si>
+    <t>Forza</t>
+  </si>
+  <si>
+    <t>Valore unico</t>
+  </si>
+  <si>
+    <t>Opzioni campo</t>
+  </si>
+  <si>
+    <t>Scheda dati per suggerimento</t>
+  </si>
+  <si>
+    <t>Campo suggerimento</t>
+  </si>
+  <si>
+    <t>Testo aiuto</t>
+  </si>
+  <si>
+    <t>Configurazione Scheda Dati</t>
+  </si>
+  <si>
+    <t>Nome Scheda Dati</t>
+  </si>
+  <si>
+    <t>Descrizione Scheda Dati</t>
+  </si>
+  <si>
+    <t>Ordina scheda per</t>
+  </si>
+  <si>
+    <t>Direzione ordinamento</t>
+  </si>
+  <si>
+    <t>Consenti modifiche</t>
+  </si>
+  <si>
+    <t>Consenti inserimenti</t>
+  </si>
+  <si>
+    <t>Consenti cancellazioni</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Filtro visibilità</t>
+  </si>
+  <si>
     <t>Data e ora</t>
   </si>
   <si>
+    <t>Sì</t>
+  </si>
+  <si>
+    <t>adesso</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Testo</t>
+  </si>
+  <si>
     <t>Testo Lungo</t>
   </si>
   <si>
-    <t>Elenco di valori (separati da virgola)</t>
-  </si>
-  <si>
-    <t>Dim. massima</t>
-  </si>
-  <si>
-    <t>Obbligatorio</t>
-  </si>
-  <si>
-    <t>Sì</t>
-  </si>
-  <si>
-    <t>Valore predefinito</t>
-  </si>
-  <si>
-    <t>adesso</t>
-  </si>
-  <si>
-    <t>Sola lettura</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Visibile</t>
-  </si>
-  <si>
-    <t>Forza</t>
-  </si>
-  <si>
-    <t>Valore unico</t>
-  </si>
-  <si>
-    <t>Opzioni campo</t>
-  </si>
-  <si>
-    <t>Scheda dati per suggerimento</t>
-  </si>
-  <si>
-    <t>Campo suggerimento</t>
-  </si>
-  <si>
-    <t>Testo aiuto</t>
-  </si>
-  <si>
-    <t>Configurazione Scheda Dati</t>
+    <t>BROGLIACCIO</t>
+  </si>
+  <si>
+    <t>Brogliaccio</t>
+  </si>
+  <si>
+    <t>Crescente</t>
+  </si>
+  <si>
+    <t>SERVIZI</t>
   </si>
   <si>
     <t>Elenco segnalibri</t>
-  </si>
-  <si>
-    <t>Nome Scheda Dati</t>
-  </si>
-  <si>
-    <t>BROGLIACCIO</t>
-  </si>
-  <si>
-    <t>Descrizione Scheda Dati</t>
-  </si>
-  <si>
-    <t>Brogliaccio</t>
-  </si>
-  <si>
-    <t>Ordina scheda per</t>
-  </si>
-  <si>
-    <t>Direzione ordinamento</t>
-  </si>
-  <si>
-    <t>Crescente</t>
-  </si>
-  <si>
-    <t>Consenti modifiche</t>
-  </si>
-  <si>
-    <t>Consenti inserimenti</t>
-  </si>
-  <si>
-    <t>Consenti cancellazioni</t>
-  </si>
-  <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>SERVIZI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
@@ -147,22 +156,23 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,56 +468,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="13.997" bestFit="true" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -515,10 +527,13 @@
       <c r="C2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -526,28 +541,32 @@
       <c r="C3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>7</v>
-      </c>
-      <c r="B5"/>
-      <c r="C5"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
       <c r="B6">
         <v>255</v>
@@ -555,179 +574,179 @@
       <c r="C6">
         <v>255</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="C8"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B11"/>
-      <c r="C11"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B14"/>
-      <c r="C14"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
         <v>21</v>
-      </c>
-      <c r="B16"/>
-      <c r="C16"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>28</v>
       </c>
       <c r="B20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>